--- a/05_Figures/F06_prediction/modules/T2/d_fcsa_I/svm/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/modules/T2/d_fcsa_I/svm/c_data/results.xlsx
@@ -551,7 +551,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.185331396785421</v>
@@ -559,10 +559,18 @@
       <c r="I3" t="n">
         <v>-0.732142857142857</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.90547263681592</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.213930348258706</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.162143050481093</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0186906245269722</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -586,6 +594,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.198920028499288</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.155567333205129</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.170675873092791</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.119365556519954</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.161698526350088</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.16692182267519</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.129342738580742</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.15595161433773</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.141554864101857</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.153288987772905</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.161440183154998</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.157340232937445</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.189398158473901</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.169400971127867</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.174413104527653</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.149050306681079</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.178366081351003</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.178797090636378</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.173021549629577</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.168111244580753</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.169061027410314</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.184919462337853</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.171333197614934</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.158824228475518</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.162869561163077</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.190117457322068</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.186178206276618</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.135652253657148</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.125316555993233</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.12989621898013</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.179948777654221</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.174482307959354</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.198091683726495</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.1400597136816</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.167673577497691</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.138073688265903</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.16863526014108</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.167621277011905</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.158074063061241</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.155465036564046</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.169558604950558</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.1334230934739</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.182259892001578</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.141606285129123</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.132081730564126</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.179441268661402</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.166507451560075</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.197769863265113</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.167922503322287</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.138712252095407</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.177300600378928</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.162314335054359</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.164392145111781</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.182027581197631</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.152556887156943</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.163762441964713</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.14461077026962</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.152154139254083</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.175274729886437</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.17644001841342</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.18186254705481</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.129713006258655</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.16423658073939</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.170069085369829</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.133705882171598</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.171059655491816</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.140874843927385</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.128148874061082</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.149188451235033</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.167252346918356</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.178234703180846</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.188888146671965</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.14272424233048</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.199341373535709</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.165774958291268</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.14097165288833</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.155619870150206</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.169860977278288</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.163281647019624</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.144271482716594</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.116824217687685</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.119648061559729</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.185699448176879</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.137862083629959</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.176198784302331</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.159673466370859</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.151353561731241</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.187923830939092</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.172567432268456</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.182490909016023</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.162264029289297</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.184662672540745</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.162324971687146</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.137200893768976</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.18511409405711</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.153081728266228</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.178790385696379</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.162803690540243</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.138307161603919</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.183425667262286</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.162781843880523</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.160529252796607</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.149773065620918</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.138865552564739</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.147669801143078</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.175618343089063</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.172509780647307</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.165805940312711</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.161816739352489</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.177343511434876</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.161925794130317</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.136931148777681</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.188264864908266</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.144820157261248</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.158868549945314</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.163662252975445</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.145537330787479</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.126368701627322</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.165980396923045</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.149939910254923</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.150853442030468</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.165971290638402</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.176594542273979</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.152179830859311</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.176396311153615</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.129586786197324</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.167284309607333</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.163404841729475</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.162792391482937</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.167670942521765</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.163619960609789</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.186426594778175</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.181440854049627</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.163666572473259</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.191421005082512</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.148931827271213</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.149228437045048</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.177626152964871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.160383303696491</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.168962591426183</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.157087267421846</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.185301714885217</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.171683912132645</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.122773847855264</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.145259458881271</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.159543844793121</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.166026305376627</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.135731026210647</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.187612001237281</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.173522941809964</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.150219614803367</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.174997748007396</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.136106826574695</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.193282024304644</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.15905782137834</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.188293299055988</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.168429630153712</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.168863889917239</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.173374587479619</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.178822821512521</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.182822238363542</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.174026669477353</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.16045336788004</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.152236118282294</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.173181663251769</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.158320968772408</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.146248929791288</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.145205817438107</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.17046814855732</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.171754893815671</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.168297760152077</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.150279216819183</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.179676401019246</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.194630293506654</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.158888672786827</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.17583315765662</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.160049438879417</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.171405196064139</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.170460793732893</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.173881313658471</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.169196957916027</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.172866886583443</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.150541288328519</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.150411451419378</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.191080341360013</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.138976146102667</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.1598532636807</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.168627096089235</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.174240793882912</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.160493190839482</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.152308264675472</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.16336913636723</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.139709993415615</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.0897192041560226</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.181435331138142</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.193668471290571</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.119394817650172</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.150741148364573</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.152466993899723</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.157608914608683</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
